--- a/data/S2014_15_FINAL.xlsx
+++ b/data/S2014_15_FINAL.xlsx
@@ -1,35 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_liga" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_1liga" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30_2liga" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KVAL" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30PRAH" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30STRC" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30JHCK" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30PLZN" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30KVRY" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30LIBE" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30HRAD" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30PARD" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30VYSO" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30JHMR" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30SVMR" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NOTES" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NOTES1" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SYSTEM" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SERIES" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CLUBS" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="META" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="10_liga" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="20_1liga" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="30_2liga" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="KVAL" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="30PRAH" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="30STRC" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="30JHCK" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="30PLZN" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="30KVRY" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="30LIBE" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="30HRAD" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="30PARD" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="30VYSO" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="30JHMR" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="30SVMR" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="NOTES" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="NOTES1" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="SYSTEM" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="SERIES" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="CLUBS" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="META" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$2</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -37,7 +40,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,8 +55,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -70,6 +77,11 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -83,11 +95,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -13242,7 +13260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13357,6 +13375,23 @@
       <c r="D5" t="inlineStr">
         <is>
           <t>H</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0031</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL L35'</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -13429,7 +13464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K225"/>
+  <dimension ref="A1:L225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13488,6 +13523,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13525,6 +13565,11 @@
           <t>14 týmů (4-col): základ + předkolo/QF/SF/finále + Play Out + baráž. Mistr: HC Verva Litvínov.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13562,6 +13607,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13599,6 +13649,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13636,6 +13691,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13673,6 +13733,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13710,6 +13775,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13747,6 +13817,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13784,6 +13859,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13821,6 +13901,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13858,6 +13943,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -13895,6 +13985,11 @@
           <t>1.liga: základ + QF/SF + Play out + baráž.</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -13932,6 +14027,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -13969,6 +14069,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0013</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -14006,6 +14111,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -14043,6 +14153,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0015</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -14080,6 +14195,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0016</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -14117,6 +14237,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0017</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -14154,6 +14279,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0018</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -14191,6 +14321,11 @@
           <t>II.liga: skupiny + QF/SF/finále + baráž o 2.ligu.</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0019</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -14228,6 +14363,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0020</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -14265,6 +14405,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0021</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -14302,6 +14447,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0022</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -14339,6 +14489,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0023</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -14376,6 +14531,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0024</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -14413,6 +14573,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -14450,6 +14615,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0026</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -14487,6 +14657,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0027</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -14524,6 +14699,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0028</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -14561,6 +14741,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0029</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -14598,6 +14783,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0030</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -14630,6 +14820,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0031</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -14667,6 +14862,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0032</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -14704,6 +14904,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0033</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -14741,6 +14946,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0034</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -14889,6 +15099,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0037</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -14958,6 +15173,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0038</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -14995,6 +15215,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0039</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -15138,6 +15363,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0043</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -15651,6 +15881,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0059</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -16127,6 +16362,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0072</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -16571,6 +16811,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0075</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -16978,6 +17223,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0086</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -17385,6 +17635,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0097</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -17792,6 +18047,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0108</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -18268,6 +18528,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0120</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -18411,6 +18676,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0123</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -18739,6 +19009,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0131</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -19294,6 +19569,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0146</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -19405,6 +19685,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0149</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -19437,6 +19722,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0150</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -19585,6 +19875,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0154</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -20066,6 +20361,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0162</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -20690,6 +20990,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0182</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -21129,6 +21434,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0206</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -21240,6 +21550,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0209</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -21677,6 +21992,11 @@
       <c r="J224" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>NODE_S2013_14_0225</t>
         </is>
       </c>
     </row>
@@ -40145,6 +40465,81 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0031</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL L35'</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S2014_15_FINAL.xlsx
+++ b/data/S2014_15_FINAL.xlsx
@@ -13464,7 +13464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L225"/>
+  <dimension ref="A1:N225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13526,6 +13526,16 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>prev_node_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
         </is>
       </c>
     </row>

--- a/data/S2014_15_FINAL.xlsx
+++ b/data/S2014_15_FINAL.xlsx
@@ -13612,6 +13612,16 @@
           <t>NODE_S2014_15_0001</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0004</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0009</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>complete</t>
@@ -13621,6 +13631,14 @@
         <is>
           <t>NODE_S2013_14_0002</t>
         </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -13696,6 +13714,16 @@
           <t>NODE_S2014_15_0003</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0005</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0009</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>complete</t>
@@ -13705,6 +13733,14 @@
         <is>
           <t>NODE_S2013_14_0004</t>
         </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -13738,6 +13774,12 @@
           <t>NODE_S2014_15_0003</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0006</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>complete</t>
@@ -13747,6 +13789,14 @@
         <is>
           <t>NODE_S2013_14_0005</t>
         </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -13780,6 +13830,16 @@
           <t>NODE_S2014_15_0003</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0008</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0007</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>complete</t>
@@ -13789,6 +13849,14 @@
         <is>
           <t>NODE_S2013_14_0006</t>
         </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -13822,6 +13890,8 @@
           <t>NODE_S2014_15_0003</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>complete</t>
@@ -13831,6 +13901,14 @@
         <is>
           <t>NODE_S2013_14_0007</t>
         </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -13864,6 +13942,8 @@
           <t>NODE_S2014_15_0003</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>complete</t>
@@ -13873,6 +13953,14 @@
         <is>
           <t>NODE_S2013_14_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -13906,6 +13994,8 @@
           <t>NODE_S2014_15_0001</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>complete</t>
@@ -13915,6 +14005,14 @@
         <is>
           <t>NODE_S2013_14_0009</t>
         </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -14032,6 +14130,16 @@
           <t>NODE_S2014_15_0011</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0013</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0017</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14041,6 +14149,14 @@
         <is>
           <t>NODE_S2013_14_0012</t>
         </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -14074,6 +14190,16 @@
           <t>NODE_S2014_15_0011</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0014</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0017</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14083,6 +14209,14 @@
         <is>
           <t>NODE_S2013_14_0013</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -14116,6 +14250,12 @@
           <t>NODE_S2014_15_0011</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0015</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14125,6 +14265,14 @@
         <is>
           <t>NODE_S2013_14_0014</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -14158,6 +14306,12 @@
           <t>NODE_S2014_15_0011</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0016</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14167,6 +14321,14 @@
         <is>
           <t>NODE_S2013_14_0015</t>
         </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -14200,6 +14362,8 @@
           <t>NODE_S2014_15_0011</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14209,6 +14373,14 @@
         <is>
           <t>NODE_S2013_14_0016</t>
         </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -14242,6 +14414,8 @@
           <t>NODE_S2014_15_0011</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14251,6 +14425,14 @@
         <is>
           <t>NODE_S2013_14_0017</t>
         </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -14536,6 +14718,12 @@
           <t>NODE_S2014_15_0019</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0025</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14545,6 +14733,14 @@
         <is>
           <t>NODE_S2013_14_0024</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -14578,6 +14774,12 @@
           <t>NODE_S2014_15_0019</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0026</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14587,6 +14789,14 @@
         <is>
           <t>NODE_S2013_14_0025</t>
         </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -14620,6 +14830,12 @@
           <t>NODE_S2014_15_0019</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0027</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14629,6 +14845,14 @@
         <is>
           <t>NODE_S2013_14_0026</t>
         </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -14662,6 +14886,8 @@
           <t>NODE_S2014_15_0019</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14671,6 +14897,14 @@
         <is>
           <t>NODE_S2013_14_0027</t>
         </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -14704,6 +14938,8 @@
           <t>NODE_S2014_15_0019</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14713,6 +14949,14 @@
         <is>
           <t>NODE_S2013_14_0028</t>
         </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -15262,10 +15506,20 @@
           <t>NODE_S2014_15_0040</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -15336,10 +15590,20 @@
           <t>NODE_S2014_15_0040</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="46">
@@ -15447,10 +15711,24 @@
           <t>NODE_S2014_15_0045</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0048</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>12 týmů</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -15484,10 +15762,24 @@
           <t>NODE_S2014_15_0045</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0053</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -15669,10 +15961,24 @@
           <t>NODE_S2014_15_0045</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0056</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -15780,10 +16086,20 @@
           <t>NODE_S2014_15_0045</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="58">
@@ -15965,10 +16281,24 @@
           <t>NODE_S2014_15_0059</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0062</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>12 týmů</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -16002,10 +16332,24 @@
           <t>NODE_S2014_15_0059</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0067</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -16187,10 +16531,24 @@
           <t>NODE_S2014_15_0059</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0070</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="69">
@@ -16298,10 +16656,20 @@
           <t>NODE_S2014_15_0059</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="72">
@@ -16446,10 +16814,24 @@
           <t>NODE_S2014_15_0072</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0075</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -16483,10 +16865,24 @@
           <t>NODE_S2014_15_0072</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0078</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="77">
@@ -16594,10 +16990,24 @@
           <t>NODE_S2014_15_0072</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0081</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="80">
@@ -16705,10 +17115,20 @@
           <t>NODE_S2014_15_0072</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -16858,10 +17278,24 @@
           <t>NODE_S2014_15_0072</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0078</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="87">
@@ -17043,10 +17477,24 @@
           <t>NODE_S2014_15_0072</t>
         </is>
       </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0081</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="92">
@@ -17154,10 +17602,20 @@
           <t>NODE_S2014_15_0072</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="95">
@@ -17270,10 +17728,24 @@
           <t>NODE_S2014_15_0072</t>
         </is>
       </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0078</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="98">
@@ -17455,10 +17927,24 @@
           <t>NODE_S2014_15_0072</t>
         </is>
       </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0081</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="103">
@@ -17566,10 +18052,20 @@
           <t>NODE_S2014_15_0072</t>
         </is>
       </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="106">
@@ -17682,10 +18178,24 @@
           <t>NODE_S2014_15_0072</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0078</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -17867,10 +18377,24 @@
           <t>NODE_S2014_15_0072</t>
         </is>
       </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0081</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N113" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="114">
@@ -17978,10 +18502,20 @@
           <t>NODE_S2014_15_0072</t>
         </is>
       </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="117">
@@ -18094,10 +18628,24 @@
           <t>NODE_S2014_15_0072</t>
         </is>
       </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0078</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N119" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="120">
@@ -18279,10 +18827,24 @@
           <t>NODE_S2014_15_0072</t>
         </is>
       </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0081</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="125">
@@ -18390,10 +18952,20 @@
           <t>NODE_S2014_15_0072</t>
         </is>
       </c>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="128">
@@ -18760,10 +19332,24 @@
           <t>NODE_S2014_15_0134</t>
         </is>
       </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0137</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>5 týmů</t>
+        </is>
+      </c>
+      <c r="N137" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="138">
@@ -18797,10 +19383,24 @@
           <t>NODE_S2014_15_0134</t>
         </is>
       </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0140</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N138" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="139">
@@ -18908,10 +19508,20 @@
           <t>NODE_S2014_15_0134</t>
         </is>
       </c>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N141" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="142">
@@ -19093,10 +19703,24 @@
           <t>NODE_S2014_15_0143</t>
         </is>
       </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0146</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N146" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="147">
@@ -19130,10 +19754,24 @@
           <t>NODE_S2014_15_0143</t>
         </is>
       </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0149</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N147" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="148">
@@ -19241,10 +19879,28 @@
           <t>NODE_S2014_15_0143</t>
         </is>
       </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0156</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0154</t>
+        </is>
+      </c>
       <c r="J150" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="151">
@@ -19352,10 +20008,20 @@
           <t>NODE_S2014_15_0143</t>
         </is>
       </c>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N153" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="154">
@@ -19426,10 +20092,20 @@
           <t>NODE_S2014_15_0143</t>
         </is>
       </c>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
       <c r="J155" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N155" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="156">
@@ -19500,10 +20176,20 @@
           <t>NODE_S2014_15_0143</t>
         </is>
       </c>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N157" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="158">
@@ -19653,10 +20339,24 @@
           <t>NODE_S2014_15_0143</t>
         </is>
       </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0146</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N161" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="162">
@@ -19806,10 +20506,24 @@
           <t>NODE_S2014_15_0162</t>
         </is>
       </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0167</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr"/>
       <c r="J165" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>12 týmů</t>
+        </is>
+      </c>
+      <c r="N165" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="166">
@@ -19843,10 +20557,20 @@
           <t>NODE_S2014_15_0162</t>
         </is>
       </c>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
       <c r="J166" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>o 9. místo</t>
+        </is>
+      </c>
+      <c r="N166" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="167">
@@ -19922,10 +20646,24 @@
           <t>NODE_S2014_15_0162</t>
         </is>
       </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0172</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr"/>
       <c r="J168" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N168" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="169">
@@ -20107,10 +20845,28 @@
           <t>NODE_S2014_15_0162</t>
         </is>
       </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0177</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0175</t>
+        </is>
+      </c>
       <c r="J173" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N173" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="174">
@@ -20218,10 +20974,20 @@
           <t>NODE_S2014_15_0162</t>
         </is>
       </c>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
       <c r="J176" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N176" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="177">
@@ -20292,10 +21058,20 @@
           <t>NODE_S2014_15_0162</t>
         </is>
       </c>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
       <c r="J178" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N178" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="179">
@@ -20408,10 +21184,24 @@
           <t>NODE_S2014_15_0162</t>
         </is>
       </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0172</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr"/>
       <c r="J181" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N181" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="182">
@@ -20593,10 +21383,28 @@
           <t>NODE_S2014_15_0162</t>
         </is>
       </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0177</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0175</t>
+        </is>
+      </c>
       <c r="J186" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N186" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="187">
@@ -20704,10 +21512,20 @@
           <t>NODE_S2014_15_0162</t>
         </is>
       </c>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
       <c r="J189" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N189" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="190">
@@ -20778,10 +21596,20 @@
           <t>NODE_S2014_15_0162</t>
         </is>
       </c>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
       <c r="J191" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N191" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="192">
@@ -21148,10 +21976,24 @@
           <t>NODE_S2014_15_0196</t>
         </is>
       </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0205</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr"/>
       <c r="J201" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>7 týmů</t>
+        </is>
+      </c>
+      <c r="N201" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="202">
@@ -21222,10 +22064,20 @@
           <t>NODE_S2014_15_0196</t>
         </is>
       </c>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" t="inlineStr"/>
       <c r="J203" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N203" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="204">
@@ -21259,10 +22111,20 @@
           <t>NODE_S2014_15_0196</t>
         </is>
       </c>
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" t="inlineStr"/>
       <c r="J204" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N204" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="205">
@@ -21333,10 +22195,20 @@
           <t>NODE_S2014_15_0196</t>
         </is>
       </c>
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" t="inlineStr"/>
       <c r="J206" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N206" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="207">
@@ -21518,10 +22390,24 @@
           <t>NODE_S2014_15_0208</t>
         </is>
       </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0212</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr"/>
       <c r="J211" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>13 týmů</t>
+        </is>
+      </c>
+      <c r="N211" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="212">
@@ -21597,10 +22483,24 @@
           <t>NODE_S2014_15_0208</t>
         </is>
       </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0217</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr"/>
       <c r="J213" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N213" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="214">
@@ -21782,10 +22682,24 @@
           <t>NODE_S2014_15_0208</t>
         </is>
       </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0220</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr"/>
       <c r="J218" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N218" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="219">
@@ -21893,10 +22807,20 @@
           <t>NODE_S2014_15_0208</t>
         </is>
       </c>
+      <c r="G221" t="inlineStr"/>
+      <c r="H221" t="inlineStr"/>
       <c r="J221" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N221" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="222">
@@ -21967,10 +22891,20 @@
           <t>NODE_S2014_15_0208</t>
         </is>
       </c>
+      <c r="G223" t="inlineStr"/>
+      <c r="H223" t="inlineStr"/>
       <c r="J223" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N223" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="224">

--- a/data/S2014_15_FINAL.xlsx
+++ b/data/S2014_15_FINAL.xlsx
@@ -830,7 +830,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -13779,7 +13779,6 @@
           <t>NODE_S2014_15_0006</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>complete</t>
@@ -13890,8 +13889,6 @@
           <t>NODE_S2014_15_0003</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>complete</t>
@@ -13942,8 +13939,6 @@
           <t>NODE_S2014_15_0003</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>complete</t>
@@ -13994,8 +13989,6 @@
           <t>NODE_S2014_15_0001</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14255,7 +14248,6 @@
           <t>NODE_S2014_15_0015</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14311,7 +14303,6 @@
           <t>NODE_S2014_15_0016</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14362,8 +14353,6 @@
           <t>NODE_S2014_15_0011</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14414,8 +14403,6 @@
           <t>NODE_S2014_15_0011</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14723,7 +14710,6 @@
           <t>NODE_S2014_15_0025</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14779,7 +14765,6 @@
           <t>NODE_S2014_15_0026</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14835,7 +14820,6 @@
           <t>NODE_S2014_15_0027</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14886,8 +14870,6 @@
           <t>NODE_S2014_15_0019</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14938,8 +14920,6 @@
           <t>NODE_S2014_15_0019</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15506,8 +15486,6 @@
           <t>NODE_S2014_15_0040</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15590,8 +15568,6 @@
           <t>NODE_S2014_15_0040</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15716,7 +15692,6 @@
           <t>NODE_S2014_15_0048</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15767,7 +15742,6 @@
           <t>NODE_S2014_15_0053</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15966,7 +15940,6 @@
           <t>NODE_S2014_15_0056</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16086,8 +16059,6 @@
           <t>NODE_S2014_15_0045</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16286,7 +16257,6 @@
           <t>NODE_S2014_15_0062</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16337,7 +16307,6 @@
           <t>NODE_S2014_15_0067</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16536,7 +16505,6 @@
           <t>NODE_S2014_15_0070</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16656,8 +16624,6 @@
           <t>NODE_S2014_15_0059</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16819,7 +16785,6 @@
           <t>NODE_S2014_15_0075</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16870,7 +16835,6 @@
           <t>NODE_S2014_15_0078</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16995,7 +16959,6 @@
           <t>NODE_S2014_15_0081</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17115,8 +17078,6 @@
           <t>NODE_S2014_15_0072</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17283,7 +17244,6 @@
           <t>NODE_S2014_15_0078</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17482,7 +17442,6 @@
           <t>NODE_S2014_15_0081</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17602,8 +17561,6 @@
           <t>NODE_S2014_15_0072</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17733,7 +17690,6 @@
           <t>NODE_S2014_15_0078</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17932,7 +17888,6 @@
           <t>NODE_S2014_15_0081</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18052,8 +18007,6 @@
           <t>NODE_S2014_15_0072</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18183,7 +18136,6 @@
           <t>NODE_S2014_15_0078</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18382,7 +18334,6 @@
           <t>NODE_S2014_15_0081</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18502,8 +18453,6 @@
           <t>NODE_S2014_15_0072</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18633,7 +18582,6 @@
           <t>NODE_S2014_15_0078</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18832,7 +18780,6 @@
           <t>NODE_S2014_15_0081</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18952,8 +18899,6 @@
           <t>NODE_S2014_15_0072</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19337,7 +19282,6 @@
           <t>NODE_S2014_15_0137</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19388,7 +19332,6 @@
           <t>NODE_S2014_15_0140</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19508,8 +19451,6 @@
           <t>NODE_S2014_15_0134</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr"/>
-      <c r="H141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19708,7 +19649,6 @@
           <t>NODE_S2014_15_0146</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19759,7 +19699,6 @@
           <t>NODE_S2014_15_0149</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20008,8 +19947,6 @@
           <t>NODE_S2014_15_0143</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr"/>
-      <c r="H153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20092,8 +20029,6 @@
           <t>NODE_S2014_15_0143</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr"/>
-      <c r="H155" t="inlineStr"/>
       <c r="J155" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20176,8 +20111,6 @@
           <t>NODE_S2014_15_0143</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr"/>
-      <c r="H157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20344,7 +20277,6 @@
           <t>NODE_S2014_15_0146</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20511,7 +20443,6 @@
           <t>NODE_S2014_15_0167</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr"/>
       <c r="J165" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20557,8 +20488,6 @@
           <t>NODE_S2014_15_0162</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr"/>
-      <c r="H166" t="inlineStr"/>
       <c r="J166" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20651,7 +20580,6 @@
           <t>NODE_S2014_15_0172</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr"/>
       <c r="J168" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20974,8 +20902,6 @@
           <t>NODE_S2014_15_0162</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr"/>
-      <c r="H176" t="inlineStr"/>
       <c r="J176" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21058,8 +20984,6 @@
           <t>NODE_S2014_15_0162</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr"/>
-      <c r="H178" t="inlineStr"/>
       <c r="J178" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21189,7 +21113,6 @@
           <t>NODE_S2014_15_0172</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr"/>
       <c r="J181" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21512,8 +21435,6 @@
           <t>NODE_S2014_15_0162</t>
         </is>
       </c>
-      <c r="G189" t="inlineStr"/>
-      <c r="H189" t="inlineStr"/>
       <c r="J189" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21596,8 +21517,6 @@
           <t>NODE_S2014_15_0162</t>
         </is>
       </c>
-      <c r="G191" t="inlineStr"/>
-      <c r="H191" t="inlineStr"/>
       <c r="J191" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21981,7 +21900,6 @@
           <t>NODE_S2014_15_0205</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr"/>
       <c r="J201" t="inlineStr">
         <is>
           <t>complete</t>
@@ -22064,8 +21982,6 @@
           <t>NODE_S2014_15_0196</t>
         </is>
       </c>
-      <c r="G203" t="inlineStr"/>
-      <c r="H203" t="inlineStr"/>
       <c r="J203" t="inlineStr">
         <is>
           <t>complete</t>
@@ -22111,8 +22027,6 @@
           <t>NODE_S2014_15_0196</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr"/>
-      <c r="H204" t="inlineStr"/>
       <c r="J204" t="inlineStr">
         <is>
           <t>complete</t>
@@ -22195,8 +22109,6 @@
           <t>NODE_S2014_15_0196</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr"/>
-      <c r="H206" t="inlineStr"/>
       <c r="J206" t="inlineStr">
         <is>
           <t>complete</t>
@@ -22395,7 +22307,6 @@
           <t>NODE_S2014_15_0212</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr"/>
       <c r="J211" t="inlineStr">
         <is>
           <t>complete</t>
@@ -22488,7 +22399,6 @@
           <t>NODE_S2014_15_0217</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr"/>
       <c r="J213" t="inlineStr">
         <is>
           <t>complete</t>
@@ -22687,7 +22597,6 @@
           <t>NODE_S2014_15_0220</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr"/>
       <c r="J218" t="inlineStr">
         <is>
           <t>complete</t>
@@ -22807,8 +22716,6 @@
           <t>NODE_S2014_15_0208</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr"/>
-      <c r="H221" t="inlineStr"/>
       <c r="J221" t="inlineStr">
         <is>
           <t>complete</t>
@@ -22891,8 +22798,6 @@
           <t>NODE_S2014_15_0208</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr"/>
-      <c r="H223" t="inlineStr"/>
       <c r="J223" t="inlineStr">
         <is>
           <t>complete</t>
@@ -41317,7 +41222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41401,6 +41306,18 @@
       <c r="B7" t="inlineStr">
         <is>
           <t>0 oprav kvalifikačních levelů. Sloupec Q (level) aktualizován.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HC Verva Litvínov</t>
         </is>
       </c>
     </row>

--- a/data/S2014_15_FINAL.xlsx
+++ b/data/S2014_15_FINAL.xlsx
@@ -6374,7 +6374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W49"/>
+  <dimension ref="A1:W69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -8999,6 +8999,836 @@
       <c r="V49" s="2" t="n"/>
       <c r="W49" s="2" t="n"/>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0227</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>HC Světlá nad Sázavou</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0227</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0273</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>TR_S2014_15_00273</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>9</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>HC Chotěboř</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0227</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0274</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>TR_S2014_15_00274</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>10</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>HC Ledeč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0227</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0275</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>TR_S2014_15_00275</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0228</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Spartak Choceň B</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0228</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0276</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>TR_S2014_15_00276</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>IHC Česká Třebová</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0228</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0277</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>TR_S2014_15_00277</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>3</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>TJ Voděrady</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0228</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0278</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>TR_S2014_15_00278</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>4</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>SK Žamberk</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0228</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0279</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>TR_S2014_15_00279</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>5</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>HC Dlouhoňovice</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0228</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0280</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>TR_S2014_15_00280</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>6</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Jiskra Králíky</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0228</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0281</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>TR_S2014_15_00281</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>7</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Sokol Řetová</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0228</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0282</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>TR_S2014_15_00282</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>AHC Čankovice</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0228</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0283</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>TR_S2014_15_00283</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>HC Bítovany</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0228</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0284</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>TR_S2014_15_00284</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Torpédo Pardubice</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0228</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0285</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>TR_S2014_15_00285</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Vysmátý zmije Pardubice</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0228</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0286</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>TR_S2014_15_00286</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>HC Hlinsko "B"</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0228</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0287</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>TR_S2014_15_00287</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Jiskra Skuteč</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0228</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0288</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>TR_S2014_15_00288</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>TJ Sokol Česká Bělá</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0228</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0289</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>TR_S2014_15_00289</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Holomci Jezbořice</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0228</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0290</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>TR_S2014_15_00290</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9010,7 +9840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W26"/>
+  <dimension ref="A1:W46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -10627,6 +11457,860 @@
       <c r="U26" s="2" t="n"/>
       <c r="V26" s="2" t="n"/>
       <c r="W26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0229</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Lokomotiva Brno</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0229</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0291</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>TR_S2014_15_00291</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>HC Veverská Bítýška</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0229</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0292</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>TR_S2014_15_00292</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>4</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>HC Zastávka</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0229</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0293</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>TR_S2014_15_00293</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0230</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>HAS Jihlava</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0230</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0294</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>TR_S2014_15_00294</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>HC Rantířov</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0230</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0295</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>TR_S2014_15_00295</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>HC Amatero Luka nad Jihlavou</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0230</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0296</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>TR_S2014_15_00296</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>HC Velký Beranov</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0230</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0297</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>TR_S2014_15_00297</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>HC Kokodáci</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0230</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0298</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>TR_S2014_15_00298</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>6</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>HC Chvojkovice – Brod</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0230</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0299</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>TR_S2014_15_00299</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>7</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>HC Fan Club Dukla Jihlava</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0230</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0300</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>TR_S2014_15_00300</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>HC Lukáš</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0230</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0301</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>TR_S2014_15_00301</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Horní Heřmanice</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0230</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0302</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>TR_S2014_15_00302</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>3</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>HPH Pokojovice</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0230</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0303</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>TR_S2014_15_00303</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>4</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Sokol Stařeč</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0230</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0304</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>TR_S2014_15_00304</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>5</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Sokol Okříšky</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0230</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0305</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>TR_S2014_15_00305</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>6</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Veselý TEAM</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0230</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0306</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>TR_S2014_15_00306</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>7</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Krhov</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0230</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0307</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>TR_S2014_15_00307</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>8</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>HC Drakstav</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0230</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0308</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>TR_S2014_15_00308</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13464,7 +15148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N225"/>
+  <dimension ref="A1:N231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22883,6 +24567,228 @@
       <c r="J225" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0225</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Praha – Pražský přebor</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>REG_PHA</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0040</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0226</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Karlovarský – Krajská liga</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>REG_KVK</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0130</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0227</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Pardubický – Krajská liga</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>REG_PAK</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0162</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0228</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Pardubický – Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>REG_PAK</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0162</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0229</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Vysočina – Krajská liga</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>REG_VYS</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0196</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0230</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Vysočina – Jihlava</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>REG_VYS</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0196</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
         </is>
       </c>
     </row>
@@ -28435,7 +30341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J270"/>
+  <dimension ref="A1:J309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="8" max="8"/>
@@ -41208,6 +43114,1059 @@
       <c r="J270" t="inlineStr">
         <is>
           <t>RT Torax Poruba</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0270</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Slovan Louny</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Slovan Louny</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>30PRAH</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0271</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>HC Roudnice nad Labem</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>HC Roudnice nad Labem</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>30PRAH</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0272</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>SK Kadaň B</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>SK Kadaň B</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>30KVRY</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0273</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>HC Světlá nad Sázavou</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>HC Světlá nad Sázavou</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0274</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>HC Chotěboř</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>HC Chotěboř</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0275</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>HC Ledeč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>HC Ledeč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0276</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Spartak Choceň B</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Spartak Choceň B</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0277</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>IHC Česká Třebová</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>IHC Česká Třebová</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0278</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>TJ Voděrady</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>TJ Voděrady</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0279</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>SK Žamberk</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>SK Žamberk</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0280</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>HC Dlouhoňovice</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>HC Dlouhoňovice</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0281</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Jiskra Králíky</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Jiskra Králíky</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0282</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Sokol Řetová</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Sokol Řetová</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0283</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>AHC Čankovice</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>AHC Čankovice</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0284</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>HC Bítovany</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>HC Bítovany</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0285</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Torpédo Pardubice</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Torpédo Pardubice</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0286</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Vysmátý zmije Pardubice</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Vysmátý zmije Pardubice</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0287</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>HC Hlinsko "B"</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>HC Hlinsko "B"</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0288</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Jiskra Skuteč</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Jiskra Skuteč</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0289</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>TJ Sokol Česká Bělá</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>TJ Sokol Česká Bělá</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0290</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Holomci Jezbořice</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Holomci Jezbořice</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0291</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Lokomotiva Brno</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Lokomotiva Brno</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0292</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>HC Veverská Bítýška</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>HC Veverská Bítýška</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0293</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>HC Zastávka</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>HC Zastávka</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0294</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>HAS Jihlava</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>HAS Jihlava</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0295</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>HC Rantířov</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>HC Rantířov</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0296</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>HC Amatero Luka nad Jihlavou</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>HC Amatero Luka nad Jihlavou</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0297</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>HC Velký Beranov</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>HC Velký Beranov</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0298</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>HC Kokodáci</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>HC Kokodáci</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0299</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>HC Chvojkovice – Brod</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>HC Chvojkovice – Brod</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0300</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>HC Fan Club Dukla Jihlava</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>HC Fan Club Dukla Jihlava</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0301</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>HC Lukáš</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>HC Lukáš</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0302</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Horní Heřmanice</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Horní Heřmanice</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0303</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>HPH Pokojovice</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>HPH Pokojovice</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0304</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Sokol Stařeč</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Sokol Stařeč</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0305</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Sokol Okříšky</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Sokol Okříšky</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0306</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Veselý TEAM</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Veselý TEAM</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0307</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Krhov</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Krhov</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0308</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>HC Drakstav</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>HC Drakstav</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>L40</t>
         </is>
       </c>
     </row>
@@ -45427,7 +48386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:W27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -47120,6 +50079,118 @@
       <c r="V24" t="inlineStr">
         <is>
           <t>TR_S2014_15_00093</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Pražský přebor</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0225</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>6</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Slovan Louny</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Pražský přebor</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0225</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0270</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>TR_S2014_15_00270</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>9</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>HC Roudnice nad Labem</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Pražský přebor</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0225</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0271</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>TR_S2014_15_00271</t>
         </is>
       </c>
     </row>
@@ -57105,7 +60176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W13"/>
+  <dimension ref="A1:W15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -58067,6 +61138,73 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0226</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SK Kadaň B</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0226</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>CLUB_S2014_15_0272</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>TR_S2014_15_00272</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/S2014_15_FINAL.xlsx
+++ b/data/S2014_15_FINAL.xlsx
@@ -40,7 +40,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,8 +59,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -82,6 +86,11 @@
         <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -95,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -106,6 +115,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -44291,7 +44302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -44348,11 +44359,63 @@
           <t>NODE_S2014_15_0031</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL L35'</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Praha – Pražský přebor (Praha) · NODE_S2014_15_0225</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>máme jen 2 týmy (Slovan Louny, HC Roudnice nad Labem), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Karlovarský – Krajská liga (Karlovarský kraj) · NODE_S2014_15_0226</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>máme jen 1 tým (SK Kadaň B), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F2"/>

--- a/data/S2014_15_FINAL.xlsx
+++ b/data/S2014_15_FINAL.xlsx
@@ -104,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -117,6 +117,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -14955,7 +14958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15085,6 +15088,40 @@
         </is>
       </c>
       <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0225</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 2 týmy (Slovan Louny, HC Roudnice nad Labem), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NODE_S2014_15_0226</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 1 tým (SK Kadaň B), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -44379,7 +44416,7 @@
           <t>Praha – Pražský přebor (Praha) · NODE_S2014_15_0225</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>máme jen 2 týmy (Slovan Louny, HC Roudnice nad Labem), chybí zbytek týmů a tabulka  [torzo-audit]</t>
         </is>
@@ -44405,7 +44442,7 @@
           <t>Karlovarský – Krajská liga (Karlovarský kraj) · NODE_S2014_15_0226</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>máme jen 1 tým (SK Kadaň B), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
         </is>

--- a/data/S2014_15_FINAL.xlsx
+++ b/data/S2014_15_FINAL.xlsx
@@ -17116,7 +17116,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>30_Praha L40</t>
+          <t>Praha, 4. úroveň</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -17322,7 +17322,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>30_Středočeský L40</t>
+          <t>Středočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -17887,7 +17887,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40</t>
+          <t>Jihočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -18061,7 +18061,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Slavoj Český Krumlov – Jiskra Humpolec  8:4,4:3</t>
+          <t>Slavoj Český Krumlov – Jiskra Humpolec 8:4,4:3</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -18098,7 +18098,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>IHC Písek – HC Strakonice   6:0,9:3</t>
+          <t>IHC Písek – HC Strakonice 6:0,9:3</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -18135,7 +18135,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Lokomotiva Veselí nad Lužnicí – HC Milevsko 2010  6:2,1:4,2:0</t>
+          <t>Lokomotiva Veselí nad Lužnicí – HC Milevsko 2010 6:2,1:4,2:0</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -18172,7 +18172,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>HC Tábor "B" - David servis České Budějovice  3:5,3:6</t>
+          <t>HC Tábor "B" - David servis České Budějovice 3:5,3:6</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -18259,7 +18259,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Slavoj Český Krumlov - David servis České Budějovice  3:1,2:3,1:3</t>
+          <t>Slavoj Český Krumlov - David servis České Budějovice 3:1,2:3,1:3</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -18378,7 +18378,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>IHC Písek - David servis České Budějovice  4:1,3:7,5:4</t>
+          <t>IHC Písek - David servis České Budějovice 4:1,3:7,5:4</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -18415,7 +18415,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40</t>
+          <t>Plzeňský, 4. úroveň</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -19444,7 +19444,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>HC JAM Plzeň- HC Saxana Group  - TJ Město Zbiroh "A" 0:7, 2:3</t>
+          <t>HC JAM Plzeň- HC Saxana Group - TJ Město Zbiroh "A" 0:7, 2:3</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -20001,7 +20001,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>TJ Sokol Lipnice – SKP Rapid Plzeň  5:1, 5:1</t>
+          <t>TJ Sokol Lipnice – SKP Rapid Plzeň 5:1, 5:1</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -20447,7 +20447,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>HC Panasonic Plzeň – TJ Sokol Díly 4:2, 1:6,  nájezdy 0:1</t>
+          <t>HC Panasonic Plzeň – TJ Sokol Díly 4:2, 1:6, nájezdy 0:1</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -20534,7 +20534,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>TJ Sokol Díly – 1.LHC Kralovice 1991  0:5 K, 0:5 K</t>
+          <t>TJ Sokol Díly – 1.LHC Kralovice 1991 0:5 K, 0:5 K</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -20653,7 +20653,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>HC Tempo Staňkov – 1.LHC Kralovice 1991  3:3, 1:2</t>
+          <t>HC Tempo Staňkov – 1.LHC Kralovice 1991 3:3, 1:2</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -20764,7 +20764,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>30_Karlovarský L40</t>
+          <t>Karlovarský, 4. úroveň</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -20912,7 +20912,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>30_Liberecký L40</t>
+          <t>Liberecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -21086,7 +21086,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>HC Česká Lípa – HC Lomnice nad Popelkou  10:6,3:8,1:4</t>
+          <t>HC Česká Lípa – HC Lomnice nad Popelkou 10:6,3:8,1:4</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -21123,7 +21123,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>PSK Liberec - VTJ Liberec  3:7,2:3 PP</t>
+          <t>PSK Liberec - VTJ Liberec 3:7,2:3 PP</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -21205,7 +21205,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>VTJ Liberec – HC Lomnice nad Popelkou  4:1,5:0 K</t>
+          <t>VTJ Liberec – HC Lomnice nad Popelkou 4:1,5:0 K</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -21279,7 +21279,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>30_Hradecký L40</t>
+          <t>Hradecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -21453,7 +21453,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Stadion Nový Bydžov – Spartak Nové Město nad Metují  6:3,7:3</t>
+          <t>Stadion Nový Bydžov – Spartak Nové Město nad Metují 6:3,7:3</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -21490,7 +21490,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SK Třebechovice pod Orebem - HC  Jičín  4:2,3:4 SN,8:4</t>
+          <t>SK Třebechovice pod Orebem - HC Jičín 4:2,3:4 SN,8:4</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -21582,7 +21582,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>HC Náchod – SK Třebechovice pod Orebem  5:1,10:2</t>
+          <t>HC Náchod – SK Třebechovice pod Orebem 5:1,10:2</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -21619,7 +21619,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>HC Jaroměř – Stadion Nový Bydžov  3:7,5:4,3:0</t>
+          <t>HC Jaroměř – Stadion Nový Bydžov 3:7,5:4,3:0</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -21701,7 +21701,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>HC Jičín – Spartak Nové Město nad Metují  2:3,0:5 K</t>
+          <t>HC Jičín – Spartak Nové Město nad Metují 2:3,0:5 K</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -21783,7 +21783,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Stadion Nový Bydžov – SK Třebechovice pod Orebem  0:5,3:8</t>
+          <t>Stadion Nový Bydžov – SK Třebechovice pod Orebem 0:5,3:8</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -21865,7 +21865,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>SK Náchod – HC Jaroměř  3:2,7:0</t>
+          <t>SK Náchod – HC Jaroměř 3:2,7:0</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -22073,7 +22073,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>30_Pardubický L40</t>
+          <t>Pardubický, 4. úroveň</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -22334,7 +22334,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Slovan Moravská Třebová – Závodní Hokejové Pardubice  14:2,10:2</t>
+          <t>Slovan Moravská Třebová – Závodní Hokejové Pardubice 14:2,10:2</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -22371,7 +22371,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>HC Litomyšl – HC Skuteč  5:1,1:2,12:1</t>
+          <t>HC Litomyšl – HC Skuteč 5:1,1:2,12:1</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -22408,7 +22408,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Spartak Polička – HC Ledeč nad Sázavou  2:8,11:3,8:2</t>
+          <t>Spartak Polička – HC Ledeč nad Sázavou 2:8,11:3,8:2</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -22445,7 +22445,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>HC Hlinsko – HC Chotěboř  3:5,4:3,2:6</t>
+          <t>HC Hlinsko – HC Chotěboř 3:5,4:3,2:6</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -22537,7 +22537,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>HC Litomyšl – Spartak Polička  1:0,5:1</t>
+          <t>HC Litomyšl – Spartak Polička 1:0,5:1</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -22574,7 +22574,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Slovan Moravská Třebová – HC Chotěboř  9:5,4:5,5:2</t>
+          <t>Slovan Moravská Třebová – HC Chotěboř 9:5,4:5,5:2</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -22656,7 +22656,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>HC Chotěboř – Spartak Polička  8:3, 8:2</t>
+          <t>HC Chotěboř – Spartak Polička 8:3, 8:2</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -22738,7 +22738,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Slovan Moravská Třebová – HC Litomyšl  5:4,4:3</t>
+          <t>Slovan Moravská Třebová – HC Litomyšl 5:4,4:3</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>HC Světlá nad Sázavou  - Spartak Polička  5:0,8:2,6:4</t>
+          <t>HC Světlá nad Sázavou - Spartak Polička 5:0,8:2,6:4</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -22941,7 +22941,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Slovan Moravská Třebová  - Kohouti Česká Třebová  2:3 PP,2:4,4:1,5:6</t>
+          <t>Slovan Moravská Třebová - Kohouti Česká Třebová 2:3 PP,2:4,4:1,5:6</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -22978,7 +22978,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Spartak Choceň  - HC Litomyšl  5:2,5:1,3:2 SN</t>
+          <t>Spartak Choceň - HC Litomyšl 5:2,5:1,3:2 SN</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -23070,7 +23070,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>HC Chrudim - Kohouti Česká Třebová  6:2,4:7,5:2,4:5 PP,4:1</t>
+          <t>HC Chrudim - Kohouti Česká Třebová 6:2,4:7,5:2,4:5 PP,4:1</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -23107,7 +23107,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>HC Světlá nad Sázavou - Spartak Choceň  3:1,4:3 PP,4:1</t>
+          <t>HC Světlá nad Sázavou - Spartak Choceň 3:1,4:3 PP,4:1</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -23189,7 +23189,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Kohouti Česká Třebová - Spartak Choceň  11:4, 7:7</t>
+          <t>Kohouti Česká Třebová - Spartak Choceň 11:4, 7:7</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -23271,7 +23271,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>HC Chrudim - HC Světlá nad Sázavou  3:5,1:7,1:4</t>
+          <t>HC Chrudim - HC Světlá nad Sázavou 3:5,1:7,1:4</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -23456,7 +23456,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>30_Vysočina L40</t>
+          <t>Vysočina, 4. úroveň</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -23863,7 +23863,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>SK Telč - Lokomotiva Brno   4:3,0:3,3:10</t>
+          <t>SK Telč - Lokomotiva Brno 4:3,0:3,3:10</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -23937,7 +23937,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40</t>
+          <t>Jihomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -24153,7 +24153,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Dynamiters Blansko HK  - HC Spartak Velká Bíteš 4:2,3:4 SN,2:3 PP</t>
+          <t>Dynamiters Blansko HK - HC Spartak Velká Bíteš 4:2,3:4 SN,2:3 PP</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -24190,7 +24190,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>HK Hokej Šumperk 2003 – TJ Šternberk   7:4,2:6,9:2</t>
+          <t>HK Hokej Šumperk 2003 – TJ Šternberk 7:4,2:6,9:2</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -24227,7 +24227,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>SK Minerva Boskovice – HHK Velké Meziříčí  2:3,5:4,6:1</t>
+          <t>SK Minerva Boskovice – HHK Velké Meziříčí 2:3,5:4,6:1</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -24264,7 +24264,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>HC Uničov – HC Štika Rosice  7:1,7:5</t>
+          <t>HC Uničov – HC Štika Rosice 7:1,7:5</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -24351,7 +24351,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>HK Hokej Šumperk 2003 – HC Spartak Velká Bíteš  2:3 PP,3:6</t>
+          <t>HK Hokej Šumperk 2003 – HC Spartak Velká Bíteš 2:3 PP,3:6</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -24388,7 +24388,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>SK Minerva Boskovice – HC Uničov  2:1,4:6,2:6</t>
+          <t>SK Minerva Boskovice – HC Uničov 2:1,4:6,2:6</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -24470,7 +24470,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>HC Uničov – HC Spartak Velká Bíteš  4:2,3:1</t>
+          <t>HC Uničov – HC Spartak Velká Bíteš 4:2,3:1</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -24552,7 +24552,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40</t>
+          <t>Severomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">

--- a/data/S2014_15_FINAL.xlsx
+++ b/data/S2014_15_FINAL.xlsx
@@ -817,7 +817,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -12628,7 +12628,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -12701,7 +12701,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -12774,7 +12774,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -12852,7 +12852,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -12925,7 +12925,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -12998,7 +12998,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -13071,7 +13071,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -13144,7 +13144,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -13217,7 +13217,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -13290,7 +13290,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -13363,7 +13363,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -13514,7 +13514,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -28438,7 +28438,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>postup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -28511,7 +28511,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -28584,7 +28584,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -28657,7 +28657,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>postup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -28735,7 +28735,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -28808,7 +28808,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -28881,7 +28881,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -28954,7 +28954,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -29027,7 +29027,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -29100,7 +29100,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -29173,7 +29173,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -29246,7 +29246,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -29324,7 +29324,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -29397,7 +29397,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>zanik</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -50596,7 +50596,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -50669,7 +50669,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -50742,7 +50742,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -50815,7 +50815,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -50888,7 +50888,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -50961,7 +50961,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -51034,7 +51034,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -51107,7 +51107,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -51180,7 +51180,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -51253,7 +51253,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -51326,7 +51326,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -51404,7 +51404,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
